--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486874_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486874_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4171</v>
+        <v>5.3338</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7824</v>
+        <v>5.5805</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3653</v>
+        <v>-0.2467</v>
       </c>
       <c r="G2" t="n">
         <v>7.709</v>
@@ -610,13 +610,13 @@
         <v>2.4641</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4474</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1198</v>
+        <v>-0.3217</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3276</v>
+        <v>-0.209</v>
       </c>
       <c r="V2" t="n">
         <v>0.825</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4551</v>
+        <v>3.7672</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5359</v>
+        <v>3.6405</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0808</v>
+        <v>0.1266</v>
       </c>
       <c r="G3" t="n">
         <v>0.8365</v>
@@ -688,13 +688,13 @@
         <v>2.4641</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8492</v>
+        <v>-1.5371</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5928</v>
+        <v>-0.4882</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.2564</v>
+        <v>-1.0489</v>
       </c>
       <c r="V3" t="n">
         <v>2.0037</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. KALU</t>
+          <t>J. CASTILLO CARRASCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7753</v>
+        <v>2.2691</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4602</v>
+        <v>1.1409</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2355</v>
+        <v>1.1282</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0391</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1268</v>
+        <v>-0.717</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1659</v>
+        <v>1.4131</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6829</v>
+        <v>1.4586</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5645</v>
+        <v>0.1168</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1184</v>
+        <v>1.3418</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3562</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6913</v>
+        <v>-0.8338</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0476</v>
+        <v>0.0713</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8748</v>
+        <v>2.0534</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2824</v>
+        <v>-0.4804</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3566</v>
+        <v>-0.3178</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0742</v>
+        <v>-0.1626</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CASTILLO CARRASCO</t>
+          <t>E. KALU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.691</v>
+        <v>1.4698</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7999000000000001</v>
+        <v>-0.4989</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8911</v>
+        <v>1.9687</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6961000000000001</v>
+        <v>1.0391</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.717</v>
+        <v>-0.1268</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4131</v>
+        <v>1.1659</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4586</v>
+        <v>0.6829</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1168</v>
+        <v>0.5645</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3418</v>
+        <v>0.1184</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7625999999999999</v>
+        <v>0.3562</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8338</v>
+        <v>-0.6913</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0713</v>
+        <v>1.0476</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0534</v>
+        <v>2.8748</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0585</v>
+        <v>-0.5879</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6587</v>
+        <v>-0.3953</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3998</v>
+        <v>-0.1925</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0698</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1555</v>
+        <v>0.9316</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7403</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5847</v>
+        <v>1.7033</v>
       </c>
       <c r="G6" t="n">
         <v>1.5595</v>
@@ -922,13 +922,13 @@
         <v>1.8481</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0949</v>
+        <v>-0.0077</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1857</v>
+        <v>-0.2171</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.2094</v>
       </c>
       <c r="V6" t="n">
         <v>0.6119</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2223</v>
+        <v>-0.645</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2536</v>
+        <v>0.6531</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4759</v>
+        <v>-1.298</v>
       </c>
       <c r="G7" t="n">
         <v>2.2007</v>
@@ -1000,13 +1000,13 @@
         <v>2.8748</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7532</v>
+        <v>-1.1758</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1431</v>
+        <v>-0.4573</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8964</v>
+        <v>-0.7185</v>
       </c>
       <c r="V7" t="n">
         <v>-3.5179</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-1.0541</v>
       </c>
       <c r="E8" t="n">
         <v>-0.2734</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4843</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>2.1605</v>
@@ -1078,13 +1078,13 @@
         <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3021</v>
+        <v>-0.5985</v>
       </c>
       <c r="T8" t="n">
         <v>-0.3952</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0931</v>
+        <v>-0.2033</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1786</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2551</v>
+        <v>-1.7995</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2139</v>
+        <v>-2.4619</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9588</v>
+        <v>0.6624</v>
       </c>
       <c r="G9" t="n">
         <v>-2.208</v>
@@ -1156,13 +1156,13 @@
         <v>1.6427</v>
       </c>
       <c r="S9" t="n">
-        <v>1.019</v>
+        <v>0.4746</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4066</v>
+        <v>0.1587</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.3159</v>
       </c>
       <c r="V9" t="n">
         <v>0.3446</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4597</v>
+        <v>-3.0051</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8252</v>
+        <v>-3.341</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3655</v>
+        <v>0.3359</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3546</v>
@@ -1234,13 +1234,13 @@
         <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9302</v>
+        <v>-0.4755</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5928</v>
+        <v>-0.1086</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3373</v>
+        <v>-0.367</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3536</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6911</v>
+        <v>-3.5272</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1865</v>
+        <v>-3.0819</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5046</v>
+        <v>-0.4453</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9984</v>
@@ -1312,13 +1312,13 @@
         <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4525</v>
+        <v>-0.2886</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2635</v>
+        <v>-0.1589</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.189</v>
+        <v>-0.1297</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2402</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6636</v>
+        <v>-6.9485</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1898</v>
+        <v>-5.4451</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4738</v>
+        <v>-1.5034</v>
       </c>
       <c r="G12" t="n">
         <v>-2.2722</v>
@@ -1390,13 +1390,13 @@
         <v>0.4107</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2699</v>
+        <v>0.985</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9603</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3096</v>
+        <v>0.28</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9384</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.866399999999999</v>
+        <v>-3.207900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.517499999999999</v>
+        <v>-4.858900000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6509</v>
+        <v>1.651</v>
       </c>
       <c r="G13" t="n">
         <v>7.3682</v>
@@ -1468,13 +1468,13 @@
         <v>20.5342</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.881499999999999</v>
+        <v>-4.2226</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.6551</v>
+        <v>-1.996300000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.2264</v>
+        <v>-2.2262</v>
       </c>
       <c r="V13" t="n">
         <v>-3.273000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9674</v>
+        <v>8.01</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7491</v>
+        <v>6.3767</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2183</v>
+        <v>1.6333</v>
       </c>
       <c r="G14" t="n">
         <v>3.7396</v>
@@ -1546,13 +1546,13 @@
         <v>2.6694</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7927</v>
+        <v>0.2499</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8563</v>
+        <v>-0.2287</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0636</v>
+        <v>0.4786</v>
       </c>
       <c r="V14" t="n">
         <v>3.4045</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>E. HERRERA SAURET</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4171</v>
+        <v>4.0433</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4317</v>
+        <v>3.5524</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9854</v>
+        <v>0.4909</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1053</v>
+        <v>0.8195</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5735</v>
+        <v>-0.2434</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4682</v>
+        <v>1.0629</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8388</v>
+        <v>0.7613</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6809</v>
+        <v>0.1168</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1579</v>
+        <v>0.6445</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7335</v>
+        <v>0.0582</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1074</v>
+        <v>-0.3602</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6261</v>
+        <v>0.4184</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8214</v>
+        <v>1.8481</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8748</v>
+        <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4905</v>
+        <v>1.0267</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6464</v>
+        <v>0.4339</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8441</v>
+        <v>0.5928</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.3573</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. HERRERA SAURET</t>
+          <t>S. GALLEGO MOGRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2805</v>
+        <v>3.5744</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5524</v>
+        <v>0.6703</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7281</v>
+        <v>2.9041</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8195</v>
+        <v>1.1135</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2434</v>
+        <v>1.5085</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0629</v>
+        <v>-0.395</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7613</v>
+        <v>2.6309</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1168</v>
+        <v>2.1447</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6445</v>
+        <v>0.4863</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0582</v>
+        <v>-1.5174</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3602</v>
+        <v>-0.6362</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4184</v>
+        <v>-0.8813</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="Q16" t="n">
+        <v>-2.0534</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.0801</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.7361</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.6433</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.6982</v>
+      </c>
+      <c r="W16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.8481</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.2638</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.4339</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.3491</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.3573</v>
-      </c>
       <c r="X16" t="n">
-        <v>-2.0082</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. GALLEGO MOGRO</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3513</v>
+        <v>3.12</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5657</v>
+        <v>0.4903</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7856</v>
+        <v>2.6297</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1135</v>
+        <v>1.1053</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5085</v>
+        <v>1.5735</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.395</v>
+        <v>-0.4682</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6309</v>
+        <v>1.8388</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1447</v>
+        <v>1.6809</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4863</v>
+        <v>0.1579</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5174</v>
+        <v>-0.7335</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6362</v>
+        <v>-0.1074</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8813</v>
+        <v>-0.6261</v>
       </c>
       <c r="P17" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R17" t="n">
-        <v>3.0801</v>
+        <v>2.8748</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5129</v>
+        <v>1.1933</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0118</v>
+        <v>0.705</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.4883</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0064</v>
+        <v>-0.0373</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5881</v>
+        <v>0.6927</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5818</v>
+        <v>-0.73</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6077</v>
@@ -1858,13 +1858,13 @@
         <v>1.0267</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.8107</v>
       </c>
       <c r="T18" t="n">
-        <v>0.368</v>
+        <v>0.4726</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4863</v>
+        <v>0.3381</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2402</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.145</v>
+        <v>-0.3106</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7324</v>
+        <v>1.4186</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8774</v>
+        <v>-1.7292</v>
       </c>
       <c r="G19" t="n">
         <v>0.8144</v>
@@ -1936,13 +1936,13 @@
         <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6217</v>
+        <v>0.4561</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4725</v>
+        <v>0.1587</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1492</v>
+        <v>0.2974</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3491</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.8425</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5901</v>
+        <v>-0.6947</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1181</v>
+        <v>-0.1478</v>
       </c>
       <c r="G20" t="n">
         <v>0.0446</v>
@@ -2014,13 +2014,13 @@
         <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.462</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2362</v>
+        <v>0.1316</v>
       </c>
       <c r="U20" t="n">
-        <v>0.36</v>
+        <v>0.3304</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9384</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8699</v>
+        <v>-2.6474</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7239</v>
+        <v>-3.5607</v>
       </c>
       <c r="F21" t="n">
-        <v>0.854</v>
+        <v>0.9133</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6466</v>
@@ -2092,13 +2092,13 @@
         <v>2.4641</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0971</v>
+        <v>0.3196</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3829</v>
+        <v>0.5461</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2858</v>
+        <v>-0.2265</v>
       </c>
       <c r="V21" t="n">
         <v>0.3491</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2955</v>
+        <v>-3.055</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4519</v>
+        <v>-3.0334</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1563</v>
+        <v>-0.0215</v>
       </c>
       <c r="G22" t="n">
         <v>-3.7259</v>
@@ -2170,13 +2170,13 @@
         <v>3.0801</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1449</v>
+        <v>0.3855</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2094</v>
+        <v>0.209</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3543</v>
+        <v>0.1765</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7679</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. RIVAS PALMER</t>
+          <t>V. PEREZ TOMAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5116</v>
+        <v>-3.9547</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6735</v>
+        <v>-4.3081</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8381</v>
+        <v>0.3534</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.629</v>
+        <v>-6.3958</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1162</v>
+        <v>-1.1645</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.5128</v>
+        <v>-5.2313</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8563</v>
+        <v>-5.0179</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.8073</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2368</v>
+        <v>-4.2105</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7726</v>
+        <v>-1.378</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4967</v>
+        <v>-0.3572</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2759</v>
+        <v>-1.0208</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0531</v>
+        <v>-0.1831</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7905</v>
+        <v>0.0774</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2626</v>
+        <v>-0.2604</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2402</v>
+        <v>2.0082</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.6591</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2402</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V. PEREZ TOMAS</t>
+          <t>D. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6259</v>
+        <v>-4.0339</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.8311</v>
+        <v>-3.2551</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2052</v>
+        <v>-0.7788</v>
       </c>
       <c r="G24" t="n">
-        <v>-6.3958</v>
+        <v>-3.629</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1645</v>
+        <v>-1.1162</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.2313</v>
+        <v>-2.5128</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.0179</v>
+        <v>-1.8563</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8073</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.2105</v>
+        <v>-1.2368</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.378</v>
+        <v>-1.7726</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3572</v>
+        <v>-0.4967</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0208</v>
+        <v>-1.2759</v>
       </c>
       <c r="P24" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.5754</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4457</v>
+        <v>-0.3721</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4087</v>
+        <v>-0.2033</v>
       </c>
       <c r="V24" t="n">
-        <v>2.0082</v>
+        <v>-0.2402</v>
       </c>
       <c r="W24" t="n">
-        <v>1.6591</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3491</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.866600000000002</v>
+        <v>3.866300000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.651100000000002</v>
+        <v>-1.650999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>5.517499999999999</v>
+        <v>5.5174</v>
       </c>
       <c r="G25" t="n">
         <v>-7.3681</v>
@@ -2374,16 +2374,16 @@
         <v>2.5135</v>
       </c>
       <c r="I25" t="n">
-        <v>-9.881699999999999</v>
+        <v>-9.8817</v>
       </c>
       <c r="J25" t="n">
         <v>9.0822</v>
       </c>
       <c r="K25" t="n">
-        <v>7.480400000000001</v>
+        <v>7.480399999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>1.6019</v>
+        <v>1.601899999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-16.4504</v>
@@ -2395,7 +2395,7 @@
         <v>-11.4836</v>
       </c>
       <c r="P25" t="n">
-        <v>3.0801</v>
+        <v>3.080100000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-20.5341</v>
@@ -2404,22 +2404,22 @@
         <v>23.6142</v>
       </c>
       <c r="S25" t="n">
-        <v>4.8814</v>
+        <v>4.881400000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2262</v>
+        <v>2.2263</v>
       </c>
       <c r="U25" t="n">
-        <v>2.6551</v>
+        <v>2.6552</v>
       </c>
       <c r="V25" t="n">
-        <v>3.273300000000001</v>
+        <v>3.2733</v>
       </c>
       <c r="W25" t="n">
         <v>7.5747</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.301600000000001</v>
+        <v>-4.3016</v>
       </c>
     </row>
   </sheetData>
